--- a/data/remove.xlsx
+++ b/data/remove.xlsx
@@ -434,7 +434,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -527,7 +527,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20260528000010,20260604000001</t>
+          <t>__REF2__,__REF3__</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>两个真实引用</t>
+          <t>删除 2、3 号两张单</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF4__</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF4__</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF4__</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -804,7 +804,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1624,7 +1624,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>20260528000010</t>
+          <t>__REF1__</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
